--- a/artfynd/A 65187-2021 artfynd.xlsx
+++ b/artfynd/A 65187-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65187-2021 artfynd.xlsx
+++ b/artfynd/A 65187-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75185520</v>
+        <v>75185529</v>
       </c>
       <c r="B2" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3286</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477606.0042538495</v>
+        <v>477789</v>
       </c>
       <c r="R2" t="n">
-        <v>7053374.017071407</v>
+        <v>7053146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>75185517</v>
       </c>
       <c r="B3" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477782.9937752501</v>
+        <v>477783</v>
       </c>
       <c r="R3" t="n">
-        <v>7053071.077394642</v>
+        <v>7053071</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75185529</v>
+        <v>75185520</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>3286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477788.8639819173</v>
+        <v>477606</v>
       </c>
       <c r="R4" t="n">
-        <v>7053145.795287254</v>
+        <v>7053374</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91509303</v>
+        <v>91509300</v>
       </c>
       <c r="B5" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,13 +1013,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477563.1391963664</v>
+        <v>477326</v>
       </c>
       <c r="R5" t="n">
-        <v>7053360.971212135</v>
+        <v>7053620</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1046,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91509308</v>
+        <v>91509303</v>
       </c>
       <c r="B6" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477619.9788379001</v>
+        <v>477563</v>
       </c>
       <c r="R6" t="n">
-        <v>7053397.056143874</v>
+        <v>7053361</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,12 +1183,7 @@
         <v>91509305</v>
       </c>
       <c r="B7" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477815.9230470713</v>
+        <v>477816</v>
       </c>
       <c r="R7" t="n">
-        <v>7053000.981328331</v>
+        <v>7053001</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1328,19 +1248,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91509300</v>
+        <v>91509308</v>
       </c>
       <c r="B8" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,13 +1316,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477326.1737017253</v>
+        <v>477620</v>
       </c>
       <c r="R8" t="n">
-        <v>7053619.832260568</v>
+        <v>7053397</v>
       </c>
       <c r="S8" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,19 +1349,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91509306</v>
+        <v>91509297</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,13 +1417,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477815.9230470713</v>
+        <v>477326</v>
       </c>
       <c r="R9" t="n">
-        <v>7053000.981328331</v>
+        <v>7053620</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,19 +1450,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91509298</v>
+        <v>91509304</v>
       </c>
       <c r="B10" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,13 +1518,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477326.1737017253</v>
+        <v>477563</v>
       </c>
       <c r="R10" t="n">
-        <v>7053619.832260568</v>
+        <v>7053361</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,19 +1551,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91509302</v>
+        <v>91509306</v>
       </c>
       <c r="B11" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,13 +1619,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477563.1391963664</v>
+        <v>477816</v>
       </c>
       <c r="R11" t="n">
-        <v>7053360.971212135</v>
+        <v>7053001</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,19 +1652,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91509304</v>
+        <v>91509307</v>
       </c>
       <c r="B12" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477563.1391963664</v>
+        <v>477620</v>
       </c>
       <c r="R12" t="n">
-        <v>7053360.971212135</v>
+        <v>7053397</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1908,19 +1753,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91509297</v>
+        <v>91509298</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477326.1737017253</v>
+        <v>477326</v>
       </c>
       <c r="R13" t="n">
-        <v>7053619.832260568</v>
+        <v>7053620</v>
       </c>
       <c r="S13" t="n">
         <v>75</v>
@@ -2024,19 +1854,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91509307</v>
+        <v>91509302</v>
       </c>
       <c r="B14" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,21 +1898,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477619.9788379001</v>
+        <v>477563</v>
       </c>
       <c r="R14" t="n">
-        <v>7053397.056143874</v>
+        <v>7053361</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2140,19 +1955,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 65187-2021 artfynd.xlsx
+++ b/artfynd/A 65187-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75185529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75185517</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75185520</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509300</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509303</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509305</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509308</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509297</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509304</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509306</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509307</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509298</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,8 +2050,28 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91509302</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>